--- a/output/第10期計画_9月作業_アンケート分析の作業状況.xlsx
+++ b/output/第10期計画_9月作業_アンケート分析の作業状況.xlsx
@@ -3950,12 +3950,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>在宅生活改善調査 問3</t>
+          <t>在宅生活改善調査（より適切と思われるサービス）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>20.4％（98票中20票）</t>
+          <t>20.2％（99票中20票）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">

--- a/output/第10期計画_9月作業_アンケート分析の作業状況.xlsx
+++ b/output/第10期計画_9月作業_アンケート分析の作業状況.xlsx
@@ -962,7 +962,7 @@
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>【個人情報の取扱い】利用者票・職員個票及び健康とくらしの調査の個票データは個人情報を含むため、リポジトリ及び成果品には格納していない。成果品に収録しているのは集計値のみである。担当者名・電話番号・メールアドレスも収録していない。</t>
+          <t>【個人情報の取扱い】利用者票・職員個票及び健康とくらしの調査の個票データは個人情報を含むため、成果品には収録せず保管もしていない。成果品に収録しているのは集計値のみである。担当者名・電話番号・メールアドレスも収録していない。</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>アンケート調査の集計・分析について作成した成果品と、そこに収めた内容を示す。規模はファイルの実物から取得している。</t>
+          <t>アンケート調査の集計・分析について作成した成果品と、そこに収めた内容を示す。規模は成果品そのものによる。</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
     <row r="13" ht="39" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>注1）規模は成果品の実物から取得している（xlsxはシート数）。注2）「第10期計画_事業所調査の照会票と確定値管理表.xlsx」は、照会票の文面と管理表の作成は終わっているが、未回答時の扱いの決定（確認事項No.8）を待って発出していないため「確認待ち」としている。注3）個票データ（利用者票・職員個票・健康とくらしの調査の個票）は成果品に収録していない。収録しているのは集計値のみである。</t>
+          <t>注1）規模は成果品そのものによる（xlsxはシート数）。注2）「第10期計画_事業所調査の照会票と確定値管理表.xlsx」は、照会票の文面と管理表の作成は終わっているが、未回答時の扱いの決定（確認事項No.8）を待って発出していないため「確認待ち」としている。注3）個票データ（利用者票・職員個票・健康とくらしの調査の個票）は成果品に収録していない。収録しているのは集計値のみである。</t>
         </is>
       </c>
     </row>
